--- a/data/input/test_meter.xlsx
+++ b/data/input/test_meter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02- Personal\08- GIKI Bootcamp\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79EF14B-C2B7-4B01-8566-FE97F391C3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4673043-D1B7-458A-8E92-394EFF209B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{86E2ADB5-5EB0-497B-A4D7-3E30CFD98396}"/>
   </bookViews>
@@ -5659,7 +5659,9 @@
       <c r="A103" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B103" s="4"/>
+      <c r="B103" s="4">
+        <v>68000</v>
+      </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
@@ -9725,49 +9727,37 @@
       <c r="A631" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="B631" s="4">
-        <v>63000</v>
-      </c>
+      <c r="B631" s="4"/>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="B632" s="5">
-        <v>63000</v>
-      </c>
+      <c r="B632" s="5"/>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="B633" s="4">
-        <v>62000</v>
-      </c>
+      <c r="B633" s="4"/>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="B634" s="5">
-        <v>61000</v>
-      </c>
+      <c r="B634" s="5"/>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="B635" s="4">
-        <v>60000</v>
-      </c>
+      <c r="B635" s="4"/>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="B636" s="5">
-        <v>57000</v>
-      </c>
+      <c r="B636" s="5"/>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" s="4" t="s">
@@ -10573,193 +10563,145 @@
       <c r="A737" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="B737" s="4">
-        <v>42000</v>
-      </c>
+      <c r="B737" s="4"/>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="B738" s="5">
-        <v>37000</v>
-      </c>
+      <c r="B738" s="5"/>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="B739" s="4">
-        <v>34000</v>
-      </c>
+      <c r="B739" s="4"/>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="B740" s="5">
-        <v>33000</v>
-      </c>
+      <c r="B740" s="5"/>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="B741" s="4">
-        <v>43000</v>
-      </c>
+      <c r="B741" s="4"/>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="B742" s="5">
-        <v>37000</v>
-      </c>
+      <c r="B742" s="5"/>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="B743" s="4">
-        <v>28000</v>
-      </c>
+      <c r="B743" s="4"/>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" s="5" t="s">
         <v>743</v>
       </c>
-      <c r="B744" s="5">
-        <v>22000</v>
-      </c>
+      <c r="B744" s="5"/>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="B745" s="4">
-        <v>23000</v>
-      </c>
+      <c r="B745" s="4"/>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="B746" s="5">
-        <v>18000</v>
-      </c>
+      <c r="B746" s="5"/>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="B747" s="4">
-        <v>17000</v>
-      </c>
+      <c r="B747" s="4"/>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="B748" s="5">
-        <v>17000</v>
-      </c>
+      <c r="B748" s="5"/>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="B749" s="4">
-        <v>20000</v>
-      </c>
+      <c r="B749" s="4"/>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="B750" s="5">
-        <v>24000</v>
-      </c>
+      <c r="B750" s="5"/>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="B751" s="4">
-        <v>29000</v>
-      </c>
+      <c r="B751" s="4"/>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" s="5" t="s">
         <v>751</v>
       </c>
-      <c r="B752" s="5">
-        <v>33000</v>
-      </c>
+      <c r="B752" s="5"/>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="B753" s="4">
-        <v>38000</v>
-      </c>
+      <c r="B753" s="4"/>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="B754" s="5">
-        <v>45000</v>
-      </c>
+      <c r="B754" s="5"/>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="B755" s="4">
-        <v>51000</v>
-      </c>
+      <c r="B755" s="4"/>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="B756" s="5">
-        <v>57000</v>
-      </c>
+      <c r="B756" s="5"/>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="B757" s="4">
-        <v>63000</v>
-      </c>
+      <c r="B757" s="4"/>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A758" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="B758" s="5">
-        <v>60000</v>
-      </c>
+      <c r="B758" s="5"/>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A759" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="B759" s="4">
-        <v>58000</v>
-      </c>
+      <c r="B759" s="4"/>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A760" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="B760" s="5">
-        <v>58000</v>
-      </c>
+      <c r="B760" s="5"/>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A761" s="4" t="s">
@@ -11565,193 +11507,145 @@
       <c r="A861" s="4" t="s">
         <v>860</v>
       </c>
-      <c r="B861" s="4">
-        <v>39000</v>
-      </c>
+      <c r="B861" s="4"/>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A862" s="5" t="s">
         <v>861</v>
       </c>
-      <c r="B862" s="5">
-        <v>44000</v>
-      </c>
+      <c r="B862" s="5"/>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A863" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="B863" s="4">
-        <v>44000</v>
-      </c>
+      <c r="B863" s="4"/>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A864" s="5" t="s">
         <v>863</v>
       </c>
-      <c r="B864" s="5">
-        <v>46000</v>
-      </c>
+      <c r="B864" s="5"/>
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A865" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="B865" s="4">
-        <v>46000</v>
-      </c>
+      <c r="B865" s="4"/>
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A866" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="B866" s="5">
-        <v>47000</v>
-      </c>
+      <c r="B866" s="5"/>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A867" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="B867" s="4">
-        <v>47000</v>
-      </c>
+      <c r="B867" s="4"/>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A868" s="5" t="s">
         <v>867</v>
       </c>
-      <c r="B868" s="5">
-        <v>47000</v>
-      </c>
+      <c r="B868" s="5"/>
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A869" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="B869" s="4">
-        <v>48000</v>
-      </c>
+      <c r="B869" s="4"/>
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A870" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="B870" s="5">
-        <v>51000</v>
-      </c>
+      <c r="B870" s="5"/>
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A871" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="B871" s="4">
-        <v>50000</v>
-      </c>
+      <c r="B871" s="4"/>
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A872" s="5" t="s">
         <v>871</v>
       </c>
-      <c r="B872" s="5">
-        <v>48000</v>
-      </c>
+      <c r="B872" s="5"/>
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A873" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="B873" s="4">
-        <v>48000</v>
-      </c>
+      <c r="B873" s="4"/>
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A874" s="5" t="s">
         <v>873</v>
       </c>
-      <c r="B874" s="5">
-        <v>47000</v>
-      </c>
+      <c r="B874" s="5"/>
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A875" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="B875" s="4">
-        <v>46000</v>
-      </c>
+      <c r="B875" s="4"/>
     </row>
     <row r="876" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A876" s="5" t="s">
         <v>875</v>
       </c>
-      <c r="B876" s="5">
-        <v>46000</v>
-      </c>
+      <c r="B876" s="5"/>
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A877" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="B877" s="4">
-        <v>44000</v>
-      </c>
+      <c r="B877" s="4"/>
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A878" s="5" t="s">
         <v>877</v>
       </c>
-      <c r="B878" s="5">
-        <v>40000</v>
-      </c>
+      <c r="B878" s="5"/>
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A879" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="B879" s="4">
-        <v>38000</v>
-      </c>
+      <c r="B879" s="4"/>
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A880" s="5" t="s">
         <v>879</v>
       </c>
-      <c r="B880" s="5">
-        <v>32000</v>
-      </c>
+      <c r="B880" s="5"/>
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A881" s="4" t="s">
         <v>880</v>
       </c>
-      <c r="B881" s="4">
-        <v>28000</v>
-      </c>
+      <c r="B881" s="4"/>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A882" s="5" t="s">
         <v>881</v>
       </c>
-      <c r="B882" s="5">
-        <v>23000</v>
-      </c>
+      <c r="B882" s="5"/>
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A883" s="4" t="s">
         <v>882</v>
       </c>
-      <c r="B883" s="4">
-        <v>19000</v>
-      </c>
+      <c r="B883" s="4"/>
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A884" s="5" t="s">
         <v>883</v>
       </c>
-      <c r="B884" s="5">
-        <v>17000</v>
-      </c>
+      <c r="B884" s="5"/>
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A885" s="4" t="s">
@@ -12677,385 +12571,289 @@
       <c r="A1000" s="5" t="s">
         <v>999</v>
       </c>
-      <c r="B1000" s="5">
-        <v>4000</v>
-      </c>
+      <c r="B1000" s="5"/>
     </row>
     <row r="1001" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1001" s="4" t="s">
         <v>1000</v>
       </c>
-      <c r="B1001" s="4">
-        <v>14000</v>
-      </c>
+      <c r="B1001" s="4"/>
     </row>
     <row r="1002" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1002" s="5" t="s">
         <v>1001</v>
       </c>
-      <c r="B1002" s="5">
-        <v>26000</v>
-      </c>
+      <c r="B1002" s="5"/>
     </row>
     <row r="1003" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1003" s="4" t="s">
         <v>1002</v>
       </c>
-      <c r="B1003" s="4">
-        <v>31000</v>
-      </c>
+      <c r="B1003" s="4"/>
     </row>
     <row r="1004" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1004" s="5" t="s">
         <v>1003</v>
       </c>
-      <c r="B1004" s="5">
-        <v>33000</v>
-      </c>
+      <c r="B1004" s="5"/>
     </row>
     <row r="1005" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1005" s="4" t="s">
         <v>1004</v>
       </c>
-      <c r="B1005" s="4">
-        <v>37000</v>
-      </c>
+      <c r="B1005" s="4"/>
     </row>
     <row r="1006" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1006" s="5" t="s">
         <v>1005</v>
       </c>
-      <c r="B1006" s="5">
-        <v>42000</v>
-      </c>
+      <c r="B1006" s="5"/>
     </row>
     <row r="1007" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1007" s="4" t="s">
         <v>1006</v>
       </c>
-      <c r="B1007" s="4">
-        <v>46000</v>
-      </c>
+      <c r="B1007" s="4"/>
     </row>
     <row r="1008" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1008" s="5" t="s">
         <v>1007</v>
       </c>
-      <c r="B1008" s="5">
-        <v>50000</v>
-      </c>
+      <c r="B1008" s="5"/>
     </row>
     <row r="1009" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1009" s="4" t="s">
         <v>1008</v>
       </c>
-      <c r="B1009" s="4">
-        <v>51000</v>
-      </c>
+      <c r="B1009" s="4"/>
     </row>
     <row r="1010" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1010" s="5" t="s">
         <v>1009</v>
       </c>
-      <c r="B1010" s="5">
-        <v>51000</v>
-      </c>
+      <c r="B1010" s="5"/>
     </row>
     <row r="1011" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1011" s="4" t="s">
         <v>1010</v>
       </c>
-      <c r="B1011" s="4">
-        <v>52000</v>
-      </c>
+      <c r="B1011" s="4"/>
     </row>
     <row r="1012" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1012" s="5" t="s">
         <v>1011</v>
       </c>
-      <c r="B1012" s="5">
-        <v>52000</v>
-      </c>
+      <c r="B1012" s="5"/>
     </row>
     <row r="1013" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1013" s="4" t="s">
         <v>1012</v>
       </c>
-      <c r="B1013" s="4">
-        <v>50000</v>
-      </c>
+      <c r="B1013" s="4"/>
     </row>
     <row r="1014" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1014" s="5" t="s">
         <v>1013</v>
       </c>
-      <c r="B1014" s="5">
-        <v>50000</v>
-      </c>
+      <c r="B1014" s="5"/>
     </row>
     <row r="1015" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1015" s="4" t="s">
         <v>1014</v>
       </c>
-      <c r="B1015" s="4">
-        <v>48000</v>
-      </c>
+      <c r="B1015" s="4"/>
     </row>
     <row r="1016" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1016" s="5" t="s">
         <v>1015</v>
       </c>
-      <c r="B1016" s="5">
-        <v>46000</v>
-      </c>
+      <c r="B1016" s="5"/>
     </row>
     <row r="1017" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1017" s="4" t="s">
         <v>1016</v>
       </c>
-      <c r="B1017" s="4">
-        <v>46000</v>
-      </c>
+      <c r="B1017" s="4"/>
     </row>
     <row r="1018" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1018" s="5" t="s">
         <v>1017</v>
       </c>
-      <c r="B1018" s="5">
-        <v>46000</v>
-      </c>
+      <c r="B1018" s="5"/>
     </row>
     <row r="1019" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1019" s="4" t="s">
         <v>1018</v>
       </c>
-      <c r="B1019" s="4">
-        <v>45000</v>
-      </c>
+      <c r="B1019" s="4"/>
     </row>
     <row r="1020" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1020" s="5" t="s">
         <v>1019</v>
       </c>
-      <c r="B1020" s="5">
-        <v>44000</v>
-      </c>
+      <c r="B1020" s="5"/>
     </row>
     <row r="1021" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1021" s="4" t="s">
         <v>1020</v>
       </c>
-      <c r="B1021" s="4">
-        <v>45000</v>
-      </c>
+      <c r="B1021" s="4"/>
     </row>
     <row r="1022" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1022" s="5" t="s">
         <v>1021</v>
       </c>
-      <c r="B1022" s="5">
-        <v>44000</v>
-      </c>
+      <c r="B1022" s="5"/>
     </row>
     <row r="1023" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1023" s="4" t="s">
         <v>1022</v>
       </c>
-      <c r="B1023" s="4">
-        <v>43000</v>
-      </c>
+      <c r="B1023" s="4"/>
     </row>
     <row r="1024" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1024" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="B1024" s="5">
-        <v>38000</v>
-      </c>
+      <c r="B1024" s="5"/>
     </row>
     <row r="1025" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1025" s="4" t="s">
         <v>1024</v>
       </c>
-      <c r="B1025" s="4">
-        <v>33000</v>
-      </c>
+      <c r="B1025" s="4"/>
     </row>
     <row r="1026" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1026" s="5" t="s">
         <v>1025</v>
       </c>
-      <c r="B1026" s="5">
-        <v>28000</v>
-      </c>
+      <c r="B1026" s="5"/>
     </row>
     <row r="1027" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1027" s="4" t="s">
         <v>1026</v>
       </c>
-      <c r="B1027" s="4">
-        <v>34000</v>
-      </c>
+      <c r="B1027" s="4"/>
     </row>
     <row r="1028" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1028" s="5" t="s">
         <v>1027</v>
       </c>
-      <c r="B1028" s="5">
-        <v>28000</v>
-      </c>
+      <c r="B1028" s="5"/>
     </row>
     <row r="1029" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1029" s="4" t="s">
         <v>1028</v>
       </c>
-      <c r="B1029" s="4">
-        <v>27000</v>
-      </c>
+      <c r="B1029" s="4"/>
     </row>
     <row r="1030" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1030" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="B1030" s="5">
-        <v>32000</v>
-      </c>
+      <c r="B1030" s="5"/>
     </row>
     <row r="1031" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1031" s="4" t="s">
         <v>1030</v>
       </c>
-      <c r="B1031" s="4">
-        <v>29000</v>
-      </c>
+      <c r="B1031" s="4"/>
     </row>
     <row r="1032" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1032" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="B1032" s="5">
-        <v>18000</v>
-      </c>
+      <c r="B1032" s="5"/>
     </row>
     <row r="1033" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1033" s="4" t="s">
         <v>1032</v>
       </c>
-      <c r="B1033" s="4">
-        <v>15000</v>
-      </c>
+      <c r="B1033" s="4"/>
     </row>
     <row r="1034" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1034" s="5" t="s">
         <v>1033</v>
       </c>
-      <c r="B1034" s="5">
-        <v>14000</v>
-      </c>
+      <c r="B1034" s="5"/>
     </row>
     <row r="1035" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1035" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="B1035" s="4">
-        <v>13000</v>
-      </c>
+      <c r="B1035" s="4"/>
     </row>
     <row r="1036" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1036" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="B1036" s="5">
-        <v>15000</v>
-      </c>
+      <c r="B1036" s="5"/>
     </row>
     <row r="1037" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1037" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="B1037" s="4">
-        <v>18000</v>
-      </c>
+      <c r="B1037" s="4"/>
     </row>
     <row r="1038" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1038" s="5" t="s">
         <v>1037</v>
       </c>
-      <c r="B1038" s="5">
-        <v>21000</v>
-      </c>
+      <c r="B1038" s="5"/>
     </row>
     <row r="1039" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1039" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="B1039" s="4">
-        <v>25000</v>
-      </c>
+      <c r="B1039" s="4"/>
     </row>
     <row r="1040" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1040" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="B1040" s="5">
-        <v>29000</v>
-      </c>
+      <c r="B1040" s="5"/>
     </row>
     <row r="1041" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1041" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="B1041" s="4">
-        <v>33000</v>
-      </c>
+      <c r="B1041" s="4"/>
     </row>
     <row r="1042" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1042" s="5" t="s">
         <v>1041</v>
       </c>
-      <c r="B1042" s="5">
-        <v>38000</v>
-      </c>
+      <c r="B1042" s="5"/>
     </row>
     <row r="1043" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1043" s="4" t="s">
         <v>1042</v>
       </c>
-      <c r="B1043" s="4">
-        <v>43000</v>
-      </c>
+      <c r="B1043" s="4"/>
     </row>
     <row r="1044" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1044" s="5" t="s">
         <v>1043</v>
       </c>
-      <c r="B1044" s="5">
-        <v>55000</v>
-      </c>
+      <c r="B1044" s="5"/>
     </row>
     <row r="1045" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1045" s="4" t="s">
         <v>1044</v>
       </c>
-      <c r="B1045" s="4">
-        <v>56000</v>
-      </c>
+      <c r="B1045" s="4"/>
     </row>
     <row r="1046" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1046" s="5" t="s">
         <v>1045</v>
       </c>
-      <c r="B1046" s="5">
-        <v>54000</v>
-      </c>
+      <c r="B1046" s="5"/>
     </row>
     <row r="1047" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1047" s="4" t="s">
         <v>1046</v>
       </c>
-      <c r="B1047" s="4">
-        <v>56000</v>
-      </c>
+      <c r="B1047" s="4"/>
     </row>
     <row r="1048" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1048" s="5" t="s">
@@ -13885,49 +13683,37 @@
       <c r="A1151" s="4" t="s">
         <v>1150</v>
       </c>
-      <c r="B1151" s="4">
-        <v>70000</v>
-      </c>
+      <c r="B1151" s="4"/>
     </row>
     <row r="1152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1152" s="5" t="s">
         <v>1151</v>
       </c>
-      <c r="B1152" s="5">
-        <v>72000</v>
-      </c>
+      <c r="B1152" s="5"/>
     </row>
     <row r="1153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1153" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="B1153" s="4">
-        <v>73000</v>
-      </c>
+      <c r="B1153" s="4"/>
     </row>
     <row r="1154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1154" s="5" t="s">
         <v>1153</v>
       </c>
-      <c r="B1154" s="5">
-        <v>72000</v>
-      </c>
+      <c r="B1154" s="5"/>
     </row>
     <row r="1155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1155" s="4" t="s">
         <v>1154</v>
       </c>
-      <c r="B1155" s="4">
-        <v>71000</v>
-      </c>
+      <c r="B1155" s="4"/>
     </row>
     <row r="1156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1156" s="5" t="s">
         <v>1155</v>
       </c>
-      <c r="B1156" s="5">
-        <v>70000</v>
-      </c>
+      <c r="B1156" s="5"/>
     </row>
     <row r="1157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1157" s="4" t="s">
@@ -14717,193 +14503,145 @@
       <c r="A1255" s="4" t="s">
         <v>1254</v>
       </c>
-      <c r="B1255" s="4">
-        <v>67000</v>
-      </c>
+      <c r="B1255" s="4"/>
     </row>
     <row r="1256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1256" s="5" t="s">
         <v>1255</v>
       </c>
-      <c r="B1256" s="5">
-        <v>64000</v>
-      </c>
+      <c r="B1256" s="5"/>
     </row>
     <row r="1257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1257" s="4" t="s">
         <v>1256</v>
       </c>
-      <c r="B1257" s="4">
-        <v>64000</v>
-      </c>
+      <c r="B1257" s="4"/>
     </row>
     <row r="1258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1258" s="5" t="s">
         <v>1257</v>
       </c>
-      <c r="B1258" s="5">
-        <v>63000</v>
-      </c>
+      <c r="B1258" s="5"/>
     </row>
     <row r="1259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1259" s="4" t="s">
         <v>1258</v>
       </c>
-      <c r="B1259" s="4">
-        <v>62000</v>
-      </c>
+      <c r="B1259" s="4"/>
     </row>
     <row r="1260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1260" s="5" t="s">
         <v>1259</v>
       </c>
-      <c r="B1260" s="5">
-        <v>61000</v>
-      </c>
+      <c r="B1260" s="5"/>
     </row>
     <row r="1261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1261" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="B1261" s="4">
-        <v>58000</v>
-      </c>
+      <c r="B1261" s="4"/>
     </row>
     <row r="1262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1262" s="5" t="s">
         <v>1261</v>
       </c>
-      <c r="B1262" s="5">
-        <v>55000</v>
-      </c>
+      <c r="B1262" s="5"/>
     </row>
     <row r="1263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1263" s="4" t="s">
         <v>1262</v>
       </c>
-      <c r="B1263" s="4">
-        <v>50000</v>
-      </c>
+      <c r="B1263" s="4"/>
     </row>
     <row r="1264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1264" s="5" t="s">
         <v>1263</v>
       </c>
-      <c r="B1264" s="5">
-        <v>44000</v>
-      </c>
+      <c r="B1264" s="5"/>
     </row>
     <row r="1265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1265" s="4" t="s">
         <v>1264</v>
       </c>
-      <c r="B1265" s="4">
-        <v>38000</v>
-      </c>
+      <c r="B1265" s="4"/>
     </row>
     <row r="1266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1266" s="5" t="s">
         <v>1265</v>
       </c>
-      <c r="B1266" s="5">
-        <v>33000</v>
-      </c>
+      <c r="B1266" s="5"/>
     </row>
     <row r="1267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1267" s="4" t="s">
         <v>1266</v>
       </c>
-      <c r="B1267" s="4">
-        <v>29000</v>
-      </c>
+      <c r="B1267" s="4"/>
     </row>
     <row r="1268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1268" s="5" t="s">
         <v>1267</v>
       </c>
-      <c r="B1268" s="5">
-        <v>26000</v>
-      </c>
+      <c r="B1268" s="5"/>
     </row>
     <row r="1269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1269" s="4" t="s">
         <v>1268</v>
       </c>
-      <c r="B1269" s="4">
-        <v>24000</v>
-      </c>
+      <c r="B1269" s="4"/>
     </row>
     <row r="1270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1270" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="B1270" s="5">
-        <v>23000</v>
-      </c>
+      <c r="B1270" s="5"/>
     </row>
     <row r="1271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1271" s="4" t="s">
         <v>1270</v>
       </c>
-      <c r="B1271" s="4">
-        <v>21000</v>
-      </c>
+      <c r="B1271" s="4"/>
     </row>
     <row r="1272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1272" s="5" t="s">
         <v>1271</v>
       </c>
-      <c r="B1272" s="5">
-        <v>20000</v>
-      </c>
+      <c r="B1272" s="5"/>
     </row>
     <row r="1273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1273" s="4" t="s">
         <v>1272</v>
       </c>
-      <c r="B1273" s="4">
-        <v>21000</v>
-      </c>
+      <c r="B1273" s="4"/>
     </row>
     <row r="1274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1274" s="5" t="s">
         <v>1273</v>
       </c>
-      <c r="B1274" s="5">
-        <v>22000</v>
-      </c>
+      <c r="B1274" s="5"/>
     </row>
     <row r="1275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1275" s="4" t="s">
         <v>1274</v>
       </c>
-      <c r="B1275" s="4">
-        <v>26000</v>
-      </c>
+      <c r="B1275" s="4"/>
     </row>
     <row r="1276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1276" s="5" t="s">
         <v>1275</v>
       </c>
-      <c r="B1276" s="5">
-        <v>25000</v>
-      </c>
+      <c r="B1276" s="5"/>
     </row>
     <row r="1277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1277" s="4" t="s">
         <v>1276</v>
       </c>
-      <c r="B1277" s="4">
-        <v>27000</v>
-      </c>
+      <c r="B1277" s="4"/>
     </row>
     <row r="1278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1278" s="5" t="s">
         <v>1277</v>
       </c>
-      <c r="B1278" s="5">
-        <v>30000</v>
-      </c>
+      <c r="B1278" s="5"/>
     </row>
     <row r="1279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1279" s="4" t="s">
